--- a/reports/2025-12-24/category_report.xlsx
+++ b/reports/2025-12-24/category_report.xlsx
@@ -413,11 +413,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -453,20 +453,229 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>BEER</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>9557.51</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10991.25</v>
+      </c>
+      <c r="D2" t="n">
+        <v>646</v>
+      </c>
+      <c r="E2" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>COOLCIDER</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5714.22</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6571.6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>450</v>
+      </c>
+      <c r="E3" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>763.9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>763.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2559</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gift Card</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>200</v>
+      </c>
+      <c r="C5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RETAIL</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>494.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>532.65</v>
+      </c>
+      <c r="D6" t="n">
+        <v>82</v>
+      </c>
+      <c r="E6" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Returns</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Rewards</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-820</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-820</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-164</v>
+      </c>
+      <c r="E8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SPIRITS</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>18751.79</v>
+      </c>
+      <c r="C9" t="n">
+        <v>21565</v>
+      </c>
+      <c r="D9" t="n">
+        <v>652</v>
+      </c>
+      <c r="E9" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WINE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3573.07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4109.11</v>
+      </c>
+      <c r="D10" t="n">
+        <v>172</v>
+      </c>
+      <c r="E10" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WINE RED</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8866.440000000001</v>
+      </c>
+      <c r="C11" t="n">
+        <v>10196.64</v>
+      </c>
+      <c r="D11" t="n">
+        <v>367</v>
+      </c>
+      <c r="E11" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WINE WHITE</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4436.04</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5101.56</v>
+      </c>
+      <c r="D12" t="n">
+        <v>234</v>
+      </c>
+      <c r="E12" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
+      <c r="B13" t="n">
+        <v>51536.87</v>
+      </c>
+      <c r="C13" t="n">
+        <v>59211.51</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4999</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1027</v>
       </c>
     </row>
   </sheetData>
